--- a/data/raw/l.AMAJ_unextracted_lines_level_logger_calibration_all.xlsx
+++ b/data/raw/l.AMAJ_unextracted_lines_level_logger_calibration_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Aliz/Documents/Doctorat/_R_Stats_PhD/connectivite/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC33848D-694D-394E-B685-2F0F48561E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DBF259-B6D2-F144-AF81-161AE87D9BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="35780" windowHeight="17240" activeTab="2" xr2:uid="{8ACBC96D-DE55-F741-9375-1F3F8F04BD26}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" activeTab="2" xr2:uid="{8ACBC96D-DE55-F741-9375-1F3F8F04BD26}"/>
   </bookViews>
   <sheets>
     <sheet name="À faire" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3328" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3380" uniqueCount="593">
   <si>
     <t>lat.garmin.dms</t>
   </si>
@@ -1780,6 +1780,45 @@
   </si>
   <si>
     <t>STH.ch2.C.p2,5m.2025</t>
+  </si>
+  <si>
+    <t>ne fonctionne pas et autres AMAJ</t>
+  </si>
+  <si>
+    <t>date démarrage en différé</t>
+  </si>
+  <si>
+    <t># sonde</t>
+  </si>
+  <si>
+    <t>site, tâche réservée</t>
+  </si>
+  <si>
+    <t>LABO</t>
+  </si>
+  <si>
+    <t>JUTRAS</t>
+  </si>
+  <si>
+    <t>niveau de pile</t>
+  </si>
+  <si>
+    <t>GRET</t>
+  </si>
+  <si>
+    <t>bon (20260210)</t>
+  </si>
+  <si>
+    <t>HOBO pendant event</t>
+  </si>
+  <si>
+    <t>Dessureault-Rompré</t>
+  </si>
+  <si>
+    <t>97% (20260210)</t>
+  </si>
+  <si>
+    <t>76% (20260210)</t>
   </si>
 </sst>
 </file>
@@ -1793,7 +1832,7 @@
     <numFmt numFmtId="167" formatCode="0.00000"/>
     <numFmt numFmtId="168" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2058,8 +2097,14 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2272,6 +2317,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2498,7 +2549,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -2617,6 +2668,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="21" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2662,7 +2723,17 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Vérification" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -25492,7 +25563,7 @@
   </sortState>
   <phoneticPr fontId="20" type="noConversion"/>
   <conditionalFormatting sqref="A21">
-    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -25525,58 +25596,61 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6DF873-63B2-F246-AFE4-C2B9E579AAD5}">
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.6640625" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="82.83203125" customWidth="1"/>
-    <col min="4" max="4" width="6.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="2"/>
-    <col min="10" max="10" width="25.1640625" customWidth="1"/>
-    <col min="11" max="11" width="26.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" style="2"/>
+    <col min="11" max="11" width="25.1640625" customWidth="1"/>
+    <col min="12" max="12" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="99" t="s">
+        <v>582</v>
+      </c>
+      <c r="B1" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="99" t="s">
         <v>308</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="99" t="s">
         <v>309</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="99" t="s">
         <v>310</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="99" t="s">
         <v>311</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="100" t="s">
+        <v>584</v>
+      </c>
+      <c r="I1" s="99" t="s">
         <v>312</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="101" t="s">
         <v>313</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="L1" s="103" t="s">
         <v>314</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="99" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>41360</v>
       </c>
@@ -25586,29 +25660,30 @@
       <c r="C2">
         <v>100</v>
       </c>
-      <c r="D2">
-        <v>7.2</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="12"/>
+      <c r="E2" s="98" t="s">
         <v>316</v>
       </c>
       <c r="F2" t="s">
         <v>255</v>
       </c>
-      <c r="H2" t="s">
-        <v>37</v>
+      <c r="H2" s="2" t="s">
+        <v>585</v>
       </c>
       <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" t="s">
         <v>69</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>317</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>41370</v>
       </c>
@@ -25618,29 +25693,30 @@
       <c r="C3">
         <v>100</v>
       </c>
-      <c r="D3">
-        <v>7.2</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F3" t="s">
         <v>255</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="I3">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>63</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>235</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>41387</v>
       </c>
@@ -25650,29 +25726,30 @@
       <c r="C4">
         <v>100</v>
       </c>
-      <c r="D4">
-        <v>7.2</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F4" t="s">
         <v>255</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="I4">
         <v>80</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>320</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>321</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>42566</v>
       </c>
@@ -25682,29 +25759,30 @@
       <c r="C5">
         <v>150</v>
       </c>
-      <c r="D5">
-        <v>7.2</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F5" t="s">
         <v>255</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="I5">
         <v>140</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>323</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>324</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>41384</v>
       </c>
@@ -25714,26 +25792,27 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6">
-        <v>7.12</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="12"/>
+      <c r="E6" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F6" t="s">
         <v>255</v>
       </c>
-      <c r="I6" t="s">
+      <c r="H6" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="J6" t="s">
         <v>325</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>239</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>41378</v>
       </c>
@@ -25743,26 +25822,27 @@
       <c r="C7">
         <v>100</v>
       </c>
-      <c r="D7">
-        <v>7.18</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="12"/>
+      <c r="E7" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F7" t="s">
         <v>255</v>
       </c>
-      <c r="I7" t="s">
+      <c r="H7" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="J7" t="s">
         <v>326</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>241</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>41368</v>
       </c>
@@ -25772,26 +25852,27 @@
       <c r="C8">
         <v>100</v>
       </c>
-      <c r="D8">
-        <v>7.19</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D8" s="12"/>
+      <c r="E8" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F8" t="s">
         <v>255</v>
       </c>
-      <c r="I8" t="s">
+      <c r="H8" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="J8" t="s">
         <v>327</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>173</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>41361</v>
       </c>
@@ -25801,26 +25882,27 @@
       <c r="C9">
         <v>100</v>
       </c>
-      <c r="D9">
-        <v>7.2</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="12"/>
+      <c r="E9" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F9" t="s">
         <v>255</v>
       </c>
-      <c r="I9" t="s">
+      <c r="H9" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="J9" t="s">
         <v>328</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>161</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>42563</v>
       </c>
@@ -25830,23 +25912,24 @@
       <c r="C10">
         <v>150</v>
       </c>
-      <c r="D10">
-        <v>7.1</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F10" t="s">
         <v>255</v>
       </c>
-      <c r="I10" t="s">
+      <c r="H10" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="J10" t="s">
         <v>329</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>41359</v>
       </c>
@@ -25856,23 +25939,24 @@
       <c r="C11">
         <v>100</v>
       </c>
-      <c r="D11">
-        <v>7.19</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="12"/>
+      <c r="E11" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F11" t="s">
         <v>255</v>
       </c>
-      <c r="I11" t="s">
+      <c r="H11" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="J11" t="s">
         <v>45</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>41383</v>
       </c>
@@ -25882,20 +25966,21 @@
       <c r="C12">
         <v>100</v>
       </c>
-      <c r="D12">
-        <v>7.12</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D12" s="12"/>
+      <c r="E12" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F12" t="s">
         <v>255</v>
       </c>
-      <c r="J12" t="s">
+      <c r="H12" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K12" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>41366</v>
       </c>
@@ -25905,20 +25990,21 @@
       <c r="C13">
         <v>100</v>
       </c>
-      <c r="D13">
-        <v>7.12</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D13" s="12"/>
+      <c r="E13" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F13" t="s">
         <v>255</v>
       </c>
-      <c r="J13" t="s">
+      <c r="H13" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K13" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>41362</v>
       </c>
@@ -25928,20 +26014,21 @@
       <c r="C14">
         <v>100</v>
       </c>
-      <c r="D14">
-        <v>7.2</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="12"/>
+      <c r="E14" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F14" t="s">
         <v>255</v>
       </c>
-      <c r="J14" t="s">
+      <c r="H14" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K14" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>42564</v>
       </c>
@@ -25951,20 +26038,21 @@
       <c r="C15">
         <v>150</v>
       </c>
-      <c r="D15">
-        <v>7.12</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D15" s="12"/>
+      <c r="E15" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F15" t="s">
         <v>255</v>
       </c>
-      <c r="J15" t="s">
+      <c r="H15" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K15" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>41374</v>
       </c>
@@ -25974,20 +26062,21 @@
       <c r="C16">
         <v>100</v>
       </c>
-      <c r="D16">
-        <v>7.14</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="D16" s="12"/>
+      <c r="E16" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F16" t="s">
         <v>255</v>
       </c>
-      <c r="J16" t="s">
+      <c r="H16" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K16" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>42562</v>
       </c>
@@ -25997,20 +26086,21 @@
       <c r="C17">
         <v>150</v>
       </c>
-      <c r="D17">
-        <v>7.2</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D17" s="12"/>
+      <c r="E17" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F17" t="s">
         <v>255</v>
       </c>
-      <c r="J17" t="s">
+      <c r="H17" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K17" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>41382</v>
       </c>
@@ -26020,20 +26110,21 @@
       <c r="C18">
         <v>100</v>
       </c>
-      <c r="D18">
-        <v>7.26</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F18" t="s">
         <v>255</v>
       </c>
-      <c r="J18" t="s">
+      <c r="H18" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K18" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>41379</v>
       </c>
@@ -26043,20 +26134,21 @@
       <c r="C19">
         <v>100</v>
       </c>
-      <c r="D19">
-        <v>7.16</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D19" s="12"/>
+      <c r="E19" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F19" t="s">
         <v>255</v>
       </c>
-      <c r="J19" t="s">
+      <c r="H19" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>42565</v>
       </c>
@@ -26066,1301 +26158,1480 @@
       <c r="C20">
         <v>150</v>
       </c>
-      <c r="D20">
-        <v>7.2</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="D20" s="12"/>
+      <c r="E20" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F20" t="s">
         <v>255</v>
       </c>
-      <c r="J20" t="s">
+      <c r="H20" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K20" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="153" x14ac:dyDescent="0.2">
-      <c r="A21" s="5"/>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>41376</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="C21">
+        <v>100</v>
+      </c>
       <c r="F21" t="s">
         <v>255</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="H21" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K21" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="9">
-        <v>41376</v>
-      </c>
-      <c r="C22">
-        <v>100</v>
-      </c>
-      <c r="D22">
-        <v>6.85</v>
-      </c>
-      <c r="E22" t="s">
-        <v>331</v>
-      </c>
-      <c r="F22" t="s">
-        <v>255</v>
-      </c>
-      <c r="J22" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="99" t="s">
+        <v>582</v>
+      </c>
+      <c r="B22" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="99" t="s">
+        <v>581</v>
+      </c>
+      <c r="D22" s="99" t="s">
+        <v>586</v>
+      </c>
+      <c r="E22" s="99" t="s">
+        <v>583</v>
+      </c>
+      <c r="F22" s="99" t="s">
+        <v>310</v>
+      </c>
+      <c r="G22" s="99" t="s">
+        <v>311</v>
+      </c>
+      <c r="H22" s="100" t="s">
+        <v>584</v>
+      </c>
+      <c r="K22" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="10"/>
-      <c r="J23" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22220787</v>
+      </c>
+      <c r="B23" t="s">
+        <v>334</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="F23" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K23" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>22220787</v>
-      </c>
-      <c r="C24" t="s">
-        <v>333</v>
-      </c>
-      <c r="D24" t="s">
+        <v>22224395</v>
+      </c>
+      <c r="B24" t="s">
         <v>334</v>
       </c>
+      <c r="C24" s="12"/>
       <c r="F24" t="s">
         <v>36</v>
       </c>
-      <c r="J24" t="s">
+      <c r="H24" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K24" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>22224395</v>
-      </c>
-      <c r="C25" t="s">
-        <v>333</v>
-      </c>
-      <c r="D25" t="s">
-        <v>334</v>
-      </c>
+        <v>22224389</v>
+      </c>
+      <c r="B25" t="s">
+        <v>336</v>
+      </c>
+      <c r="C25" s="12"/>
       <c r="F25" t="s">
         <v>36</v>
       </c>
-      <c r="J25" t="s">
+      <c r="H25" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K25" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>22224389</v>
-      </c>
-      <c r="C26" t="s">
-        <v>335</v>
-      </c>
-      <c r="D26" t="s">
+        <v>22224408</v>
+      </c>
+      <c r="B26" t="s">
         <v>336</v>
       </c>
+      <c r="C26" s="12"/>
       <c r="F26" t="s">
         <v>36</v>
       </c>
-      <c r="J26" t="s">
+      <c r="H26" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K26" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>22224408</v>
-      </c>
-      <c r="C27" t="s">
-        <v>333</v>
-      </c>
-      <c r="D27" t="s">
+        <v>22224409</v>
+      </c>
+      <c r="B27" t="s">
         <v>336</v>
       </c>
+      <c r="C27" s="12"/>
       <c r="F27" t="s">
         <v>36</v>
       </c>
-      <c r="J27" t="s">
+      <c r="H27" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K27" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>22224409</v>
-      </c>
-      <c r="C28" t="s">
-        <v>333</v>
-      </c>
-      <c r="D28" t="s">
+        <v>22220790</v>
+      </c>
+      <c r="B28" t="s">
         <v>336</v>
       </c>
+      <c r="C28" s="12"/>
       <c r="F28" t="s">
         <v>36</v>
       </c>
-      <c r="J28" t="s">
+      <c r="H28" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K28" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>22220790</v>
-      </c>
-      <c r="C29" t="s">
-        <v>333</v>
-      </c>
-      <c r="D29" t="s">
+        <v>22224393</v>
+      </c>
+      <c r="B29" t="s">
         <v>336</v>
       </c>
+      <c r="C29" s="12"/>
       <c r="F29" t="s">
         <v>36</v>
       </c>
-      <c r="J29" t="s">
+      <c r="H29" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K29" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>22224393</v>
-      </c>
-      <c r="C30" t="s">
-        <v>333</v>
-      </c>
-      <c r="D30" t="s">
+        <v>22220788</v>
+      </c>
+      <c r="B30" t="s">
         <v>336</v>
       </c>
+      <c r="C30" s="62"/>
       <c r="F30" t="s">
         <v>36</v>
       </c>
-      <c r="J30" t="s">
+      <c r="G30" t="s">
+        <v>337</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K30" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="5">
-        <v>22220788</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D31" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>22224390</v>
+      </c>
+      <c r="B31" t="s">
         <v>336</v>
       </c>
+      <c r="C31" s="62"/>
       <c r="F31" t="s">
         <v>36</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="H31" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K31" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>22224390</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D32" t="s">
+        <v>22224401</v>
+      </c>
+      <c r="B32" t="s">
         <v>336</v>
       </c>
+      <c r="C32" s="62"/>
       <c r="F32" t="s">
         <v>36</v>
       </c>
-      <c r="J32" t="s">
+      <c r="H32" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K32" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>22224401</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D33" t="s">
+        <v>22224414</v>
+      </c>
+      <c r="B33" t="s">
         <v>336</v>
       </c>
+      <c r="C33" s="62"/>
       <c r="F33" t="s">
         <v>36</v>
       </c>
-      <c r="J33" t="s">
+      <c r="H33" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K33" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>22224414</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D34" t="s">
+        <v>22224413</v>
+      </c>
+      <c r="B34" t="s">
         <v>336</v>
       </c>
+      <c r="C34" s="62"/>
       <c r="F34" t="s">
         <v>36</v>
       </c>
-      <c r="J34" t="s">
+      <c r="H34" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K34" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>22224413</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D35" t="s">
+        <v>22224403</v>
+      </c>
+      <c r="B35" t="s">
         <v>336</v>
       </c>
+      <c r="C35" s="62"/>
       <c r="F35" t="s">
         <v>36</v>
       </c>
-      <c r="J35" t="s">
+      <c r="H35" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K35" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>22224403</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D36" t="s">
+        <v>22220789</v>
+      </c>
+      <c r="B36" t="s">
         <v>336</v>
       </c>
+      <c r="C36" s="62"/>
       <c r="F36" t="s">
         <v>36</v>
       </c>
-      <c r="J36" t="s">
+      <c r="G36" t="s">
+        <v>337</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K36" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="5">
-        <v>22220789</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D37" t="s">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>22224405</v>
+      </c>
+      <c r="B37" t="s">
         <v>336</v>
       </c>
+      <c r="C37" s="62"/>
       <c r="F37" t="s">
         <v>36</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="J37" t="s">
+      <c r="H37" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K37" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>22224405</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D38" t="s">
+        <v>22224411</v>
+      </c>
+      <c r="B38" t="s">
         <v>336</v>
       </c>
+      <c r="C38" s="62"/>
       <c r="F38" t="s">
         <v>36</v>
       </c>
-      <c r="J38" t="s">
+      <c r="H38" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K38" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>22224411</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D39" t="s">
+        <v>22220783</v>
+      </c>
+      <c r="B39" t="s">
         <v>336</v>
       </c>
+      <c r="C39" s="62"/>
       <c r="F39" t="s">
         <v>36</v>
       </c>
-      <c r="J39" t="s">
+      <c r="H39" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K39" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>22220783</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D40" t="s">
+        <v>22220782</v>
+      </c>
+      <c r="B40" t="s">
         <v>336</v>
       </c>
+      <c r="C40" s="62"/>
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="J40" t="s">
+      <c r="H40" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K40" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>22220782</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D41" t="s">
+        <v>22224397</v>
+      </c>
+      <c r="B41" t="s">
         <v>336</v>
       </c>
+      <c r="C41" s="62"/>
       <c r="F41" t="s">
         <v>36</v>
       </c>
-      <c r="J41" t="s">
+      <c r="H41" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K41" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>22224397</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D42" t="s">
+        <v>22224399</v>
+      </c>
+      <c r="B42" t="s">
         <v>336</v>
       </c>
+      <c r="C42" s="62"/>
       <c r="F42" t="s">
         <v>36</v>
       </c>
-      <c r="J42" t="s">
+      <c r="H42" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K42" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>22224399</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D43" t="s">
+        <v>22224412</v>
+      </c>
+      <c r="B43" t="s">
         <v>336</v>
       </c>
+      <c r="C43" s="62"/>
       <c r="F43" t="s">
         <v>36</v>
       </c>
-      <c r="J43" t="s">
+      <c r="H43" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K43" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>22224412</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D44" t="s">
+        <v>22224400</v>
+      </c>
+      <c r="B44" t="s">
         <v>336</v>
       </c>
+      <c r="C44" s="62"/>
       <c r="F44" t="s">
         <v>36</v>
       </c>
-      <c r="J44" t="s">
+      <c r="H44" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K44" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>22224400</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D45" t="s">
+        <v>22220791</v>
+      </c>
+      <c r="B45" t="s">
         <v>336</v>
       </c>
+      <c r="C45" s="62"/>
       <c r="F45" t="s">
         <v>36</v>
       </c>
-      <c r="J45" t="s">
+      <c r="H45" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K45" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>22220791</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D46" t="s">
+        <v>22224386</v>
+      </c>
+      <c r="B46" t="s">
         <v>336</v>
       </c>
+      <c r="C46" s="62"/>
       <c r="F46" t="s">
         <v>36</v>
       </c>
-      <c r="J46" t="s">
+      <c r="G46" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K46" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A47" s="9">
-        <v>22224386</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D47" t="s">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>22224387</v>
+      </c>
+      <c r="B47" t="s">
         <v>336</v>
       </c>
+      <c r="C47" s="62"/>
       <c r="F47" t="s">
         <v>36</v>
       </c>
-      <c r="G47" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="J47" t="s">
+      <c r="H47" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K47" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>22224387</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D48" t="s">
+        <v>22224388</v>
+      </c>
+      <c r="B48" t="s">
         <v>336</v>
       </c>
+      <c r="C48" s="62"/>
       <c r="F48" t="s">
         <v>36</v>
       </c>
-      <c r="J48" t="s">
+      <c r="H48" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K48" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>22224388</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D49" t="s">
+        <v>22224394</v>
+      </c>
+      <c r="B49" t="s">
         <v>336</v>
       </c>
+      <c r="C49" s="62"/>
       <c r="F49" t="s">
         <v>36</v>
       </c>
-      <c r="J49" t="s">
+      <c r="H49" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K49" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>22224394</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D50" t="s">
+        <v>22224410</v>
+      </c>
+      <c r="B50" t="s">
         <v>336</v>
       </c>
+      <c r="C50" s="62"/>
       <c r="F50" t="s">
         <v>36</v>
       </c>
-      <c r="J50" t="s">
+      <c r="H50" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K50" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>22224410</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D51" t="s">
+        <v>22220786</v>
+      </c>
+      <c r="B51" t="s">
         <v>336</v>
       </c>
+      <c r="C51" s="62"/>
       <c r="F51" t="s">
         <v>36</v>
       </c>
-      <c r="J51" t="s">
+      <c r="H51" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K51" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>22220786</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D52" t="s">
+        <v>22224391</v>
+      </c>
+      <c r="B52" t="s">
         <v>336</v>
       </c>
+      <c r="C52" s="62"/>
       <c r="F52" t="s">
         <v>36</v>
       </c>
-      <c r="J52" t="s">
+      <c r="H52" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K52" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>22224391</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D53" t="s">
+        <v>22224392</v>
+      </c>
+      <c r="B53" t="s">
         <v>336</v>
       </c>
+      <c r="C53" s="62"/>
       <c r="F53" t="s">
         <v>36</v>
       </c>
-      <c r="J53" t="s">
+      <c r="G53" s="8"/>
+      <c r="H53" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K53" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>22224392</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D54" t="s">
+        <v>22224406</v>
+      </c>
+      <c r="B54" t="s">
         <v>336</v>
       </c>
+      <c r="C54" s="62"/>
       <c r="F54" t="s">
         <v>36</v>
       </c>
-      <c r="G54" s="21"/>
-      <c r="J54" t="s">
+      <c r="H54" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K54" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>22224406</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D55" t="s">
+        <v>22195240</v>
+      </c>
+      <c r="B55" t="s">
         <v>336</v>
       </c>
+      <c r="C55" s="62"/>
       <c r="F55" t="s">
         <v>36</v>
       </c>
-      <c r="J55" t="s">
+      <c r="G55" s="8"/>
+      <c r="H55" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K55" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>22195240</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D56" t="s">
+        <v>22063159</v>
+      </c>
+      <c r="B56" t="s">
         <v>336</v>
       </c>
+      <c r="C56" s="62"/>
       <c r="F56" t="s">
         <v>36</v>
       </c>
-      <c r="G56" s="21"/>
-      <c r="J56" t="s">
+      <c r="H56" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K56" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>22063159</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D57" t="s">
+        <v>22063156</v>
+      </c>
+      <c r="B57" t="s">
         <v>336</v>
       </c>
+      <c r="C57" s="62"/>
       <c r="F57" t="s">
         <v>36</v>
       </c>
-      <c r="J57" t="s">
+      <c r="H57" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K57" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>22063156</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D58" t="s">
+        <v>22224396</v>
+      </c>
+      <c r="B58" t="s">
         <v>336</v>
       </c>
+      <c r="C58" s="62"/>
       <c r="F58" t="s">
         <v>36</v>
       </c>
-      <c r="J58" t="s">
+      <c r="H58" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K58" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>22224396</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="D59" t="s">
+        <v>22220781</v>
+      </c>
+      <c r="B59" t="s">
         <v>336</v>
       </c>
+      <c r="C59" s="62"/>
       <c r="F59" t="s">
         <v>36</v>
       </c>
-      <c r="J59" t="s">
+      <c r="H59" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K59" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>22220781</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="D60" t="s">
+        <v>22195245</v>
+      </c>
+      <c r="B60" t="s">
         <v>336</v>
       </c>
+      <c r="C60" s="12"/>
       <c r="F60" t="s">
         <v>36</v>
       </c>
-      <c r="J60" t="s">
+      <c r="H60" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K60" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>22195245</v>
-      </c>
-      <c r="C61" t="s">
-        <v>359</v>
-      </c>
-      <c r="D61" t="s">
+        <v>22195242</v>
+      </c>
+      <c r="B61" t="s">
         <v>336</v>
       </c>
+      <c r="C61" s="62"/>
       <c r="F61" t="s">
         <v>36</v>
       </c>
-      <c r="J61" t="s">
+      <c r="H61" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K61" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>22195242</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="D62" t="s">
+        <v>22195243</v>
+      </c>
+      <c r="B62" t="s">
         <v>336</v>
       </c>
+      <c r="C62" s="12"/>
       <c r="F62" t="s">
         <v>36</v>
       </c>
-      <c r="J62" t="s">
+      <c r="H62" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K62" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>22195243</v>
-      </c>
-      <c r="C63" t="s">
-        <v>359</v>
-      </c>
-      <c r="D63" t="s">
+        <v>22195244</v>
+      </c>
+      <c r="B63" t="s">
         <v>336</v>
       </c>
+      <c r="C63" s="62"/>
       <c r="F63" t="s">
         <v>36</v>
       </c>
-      <c r="J63" t="s">
+      <c r="H63" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K63" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>22195244</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="D64" t="s">
+        <v>22195246</v>
+      </c>
+      <c r="B64" t="s">
         <v>336</v>
       </c>
+      <c r="C64" s="12"/>
       <c r="F64" t="s">
         <v>36</v>
       </c>
-      <c r="J64" t="s">
+      <c r="H64" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K64" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>22195246</v>
-      </c>
-      <c r="C65" t="s">
-        <v>359</v>
-      </c>
-      <c r="D65" t="s">
+        <v>22195247</v>
+      </c>
+      <c r="B65" t="s">
         <v>336</v>
       </c>
+      <c r="C65" s="62"/>
       <c r="F65" t="s">
         <v>36</v>
       </c>
-      <c r="J65" t="s">
+      <c r="G65" t="s">
+        <v>337</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K65" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A66" s="5">
-        <v>22195247</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="D66" t="s">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>22195248</v>
+      </c>
+      <c r="B66" t="s">
         <v>336</v>
       </c>
+      <c r="C66" s="12"/>
       <c r="F66" t="s">
         <v>36</v>
       </c>
-      <c r="G66" s="24" t="s">
-        <v>337</v>
-      </c>
-      <c r="J66" t="s">
+      <c r="H66" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K66" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>22195248</v>
-      </c>
-      <c r="C67" t="s">
-        <v>364</v>
-      </c>
-      <c r="D67" t="s">
+        <v>22063137</v>
+      </c>
+      <c r="B67" t="s">
         <v>336</v>
       </c>
+      <c r="C67" s="62"/>
+      <c r="E67" s="20"/>
       <c r="F67" t="s">
         <v>36</v>
       </c>
-      <c r="J67" t="s">
+      <c r="H67" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K67" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>22063137</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="D68" t="s">
+        <v>22063138</v>
+      </c>
+      <c r="B68" t="s">
         <v>336</v>
       </c>
+      <c r="C68" s="12"/>
       <c r="E68" s="20"/>
       <c r="F68" t="s">
         <v>36</v>
       </c>
-      <c r="J68" t="s">
+      <c r="H68" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K68" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>22063138</v>
-      </c>
-      <c r="C69" t="s">
-        <v>364</v>
-      </c>
-      <c r="D69" t="s">
+        <v>22063139</v>
+      </c>
+      <c r="B69" t="s">
         <v>336</v>
       </c>
-      <c r="E69" s="20"/>
+      <c r="C69" s="12"/>
+      <c r="E69" s="17"/>
       <c r="F69" t="s">
         <v>36</v>
       </c>
-      <c r="J69" t="s">
+      <c r="H69" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K69" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>22063139</v>
-      </c>
-      <c r="C70" t="s">
-        <v>372</v>
-      </c>
-      <c r="D70" t="s">
+        <v>22063142</v>
+      </c>
+      <c r="B70" t="s">
         <v>336</v>
       </c>
-      <c r="E70" s="17"/>
+      <c r="C70" s="12"/>
       <c r="F70" t="s">
         <v>36</v>
       </c>
-      <c r="J70" t="s">
+      <c r="H70" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K70" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>22063142</v>
-      </c>
-      <c r="C71" t="s">
-        <v>374</v>
-      </c>
-      <c r="D71" t="s">
+        <v>22063155</v>
+      </c>
+      <c r="B71" t="s">
         <v>336</v>
       </c>
+      <c r="C71" s="12"/>
       <c r="F71" t="s">
         <v>36</v>
       </c>
-      <c r="J71" t="s">
+      <c r="H71" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K71" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>22063155</v>
-      </c>
-      <c r="C72" t="s">
-        <v>364</v>
-      </c>
-      <c r="D72" t="s">
+        <v>22063141</v>
+      </c>
+      <c r="B72" t="s">
         <v>336</v>
       </c>
+      <c r="C72" s="62"/>
       <c r="F72" t="s">
         <v>36</v>
       </c>
-      <c r="J72" t="s">
+      <c r="G72" t="s">
+        <v>377</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K72" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A73" s="23">
-        <v>22063141</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="D73" t="s">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>22063143</v>
+      </c>
+      <c r="B73" t="s">
         <v>336</v>
       </c>
+      <c r="C73" s="12"/>
       <c r="F73" t="s">
         <v>36</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="J73" t="s">
+      <c r="H73" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K73" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>22063143</v>
-      </c>
-      <c r="C74" t="s">
-        <v>364</v>
-      </c>
-      <c r="D74" t="s">
+        <v>22063140</v>
+      </c>
+      <c r="B74" t="s">
         <v>336</v>
       </c>
+      <c r="C74" s="12"/>
       <c r="F74" t="s">
         <v>36</v>
       </c>
-      <c r="J74" s="17" t="s">
+      <c r="H74" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K74" s="17" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>22063140</v>
-      </c>
-      <c r="C75" t="s">
-        <v>364</v>
-      </c>
-      <c r="D75" t="s">
+        <v>22220785</v>
+      </c>
+      <c r="B75" t="s">
         <v>336</v>
       </c>
+      <c r="C75" s="12"/>
       <c r="F75" t="s">
         <v>36</v>
       </c>
-      <c r="J75" t="s">
+      <c r="G75" s="8"/>
+      <c r="H75" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K75" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>22220785</v>
-      </c>
-      <c r="C76" t="s">
-        <v>379</v>
-      </c>
-      <c r="D76" t="s">
+        <v>22220784</v>
+      </c>
+      <c r="B76" t="s">
         <v>336</v>
       </c>
+      <c r="C76" s="12"/>
       <c r="F76" t="s">
         <v>36</v>
       </c>
-      <c r="G76" s="21"/>
-      <c r="J76" t="s">
+      <c r="G76" s="8"/>
+      <c r="H76" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K76" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>22220784</v>
-      </c>
-      <c r="C77" t="s">
-        <v>379</v>
-      </c>
-      <c r="D77" t="s">
+        <v>22195241</v>
+      </c>
+      <c r="C77" s="12"/>
+      <c r="H77" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K77" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>22224381</v>
+      </c>
+      <c r="B78" t="s">
         <v>336</v>
       </c>
-      <c r="F77" t="s">
+      <c r="C78" s="62"/>
+      <c r="F78" t="s">
         <v>36</v>
       </c>
-      <c r="G77" s="21"/>
-      <c r="J77" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A78">
-        <v>22195241</v>
-      </c>
-      <c r="C78" t="s">
-        <v>379</v>
-      </c>
-      <c r="D78" s="12"/>
-      <c r="J78" t="s">
+      <c r="G78" s="13"/>
+      <c r="H78" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K78" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>22224381</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D79" t="s">
+        <v>22224407</v>
+      </c>
+      <c r="B79" t="s">
         <v>336</v>
       </c>
+      <c r="C79" s="62"/>
       <c r="F79" t="s">
         <v>36</v>
       </c>
-      <c r="G79" s="13"/>
-      <c r="J79" t="s">
+      <c r="G79" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K79" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A80" s="9">
-        <v>22224407</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D80" t="s">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>22224385</v>
+      </c>
+      <c r="B80" t="s">
         <v>336</v>
       </c>
+      <c r="C80" s="62"/>
       <c r="F80" t="s">
         <v>36</v>
       </c>
-      <c r="G80" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="J80" t="s">
+      <c r="G80" t="s">
+        <v>380</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K80" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A81" s="23">
-        <v>22224385</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="D81" t="s">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>22224402</v>
+      </c>
+      <c r="B81" t="s">
         <v>336</v>
       </c>
+      <c r="C81" s="62"/>
       <c r="F81" t="s">
         <v>36</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G81" t="s">
         <v>380</v>
       </c>
-      <c r="J81" t="s">
+      <c r="H81" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K81" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A82" s="23">
-        <v>22224402</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="D82" t="s">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>22224384</v>
+      </c>
+      <c r="B82" t="s">
         <v>336</v>
       </c>
+      <c r="C82" s="62"/>
       <c r="F82" t="s">
         <v>36</v>
       </c>
-      <c r="G82" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="J82" t="s">
+      <c r="H82" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="K82" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A83">
-        <v>22224384</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="D83" t="s">
-        <v>336</v>
-      </c>
-      <c r="F83" t="s">
-        <v>36</v>
-      </c>
-      <c r="J83" t="s">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A83" s="13"/>
+      <c r="K83" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A84" s="13"/>
-      <c r="B84" s="13"/>
-      <c r="J84" t="s">
+      <c r="C84" s="25"/>
+      <c r="K84" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="27" x14ac:dyDescent="0.35">
-      <c r="A85" s="13"/>
-      <c r="B85" s="13"/>
-      <c r="C85" s="25"/>
-      <c r="J85" t="s">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K85" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="13"/>
-      <c r="B86" s="13"/>
-      <c r="J86" t="s">
+      <c r="K86" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A87" s="13"/>
-      <c r="B87" s="13"/>
-      <c r="J87" s="13" t="s">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A87" s="13">
+        <v>22000555</v>
+      </c>
+      <c r="D87" t="s">
+        <v>588</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K87" s="13" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A88" s="14"/>
-      <c r="B88" s="13"/>
-      <c r="J88" s="13" t="s">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A88" s="14">
+        <v>22000558</v>
+      </c>
+      <c r="D88" t="s">
+        <v>588</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K88" s="13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J89" t="s">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>22030344</v>
+      </c>
+      <c r="D89" t="s">
+        <v>588</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K89" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J90" t="s">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A90" s="13">
+        <v>21981582</v>
+      </c>
+      <c r="D90" t="s">
+        <v>588</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K90" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J91" t="s">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A91" s="13">
+        <v>22030341</v>
+      </c>
+      <c r="D91" t="s">
+        <v>588</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K91" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J92" s="13" t="s">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>21157483</v>
+      </c>
+      <c r="D92" t="s">
+        <v>588</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K92" s="13" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J93" s="17" t="s">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>22030339</v>
+      </c>
+      <c r="D93" t="s">
+        <v>588</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K93" s="17" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J94" s="17" t="s">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>22000554</v>
+      </c>
+      <c r="D94" t="s">
+        <v>588</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K94" s="17" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J95" s="17" t="s">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>21981579</v>
+      </c>
+      <c r="D95" t="s">
+        <v>588</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K95" s="17" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J96" s="17" t="s">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>22024017</v>
+      </c>
+      <c r="D96" t="s">
+        <v>588</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K96" s="17" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="97" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J97" s="17" t="s">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H97" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="K97" s="17" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="98" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J98" s="17" t="s">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>10727155</v>
+      </c>
+      <c r="D98" t="s">
+        <v>591</v>
+      </c>
+      <c r="F98" t="s">
+        <v>589</v>
+      </c>
+      <c r="H98" s="104" t="s">
+        <v>590</v>
+      </c>
+      <c r="K98" s="17" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="99" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J99" s="17" t="s">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>10127026</v>
+      </c>
+      <c r="D99" s="105" t="s">
+        <v>592</v>
+      </c>
+      <c r="F99" t="s">
+        <v>589</v>
+      </c>
+      <c r="H99" s="104" t="s">
+        <v>590</v>
+      </c>
+      <c r="K99" s="17" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="100" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J100" s="17" t="s">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K100" s="17" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="102" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J102" t="s">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K102" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="103" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J103" s="22" t="s">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K103" s="22" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="104" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J104" s="22" t="s">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K104" s="22" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="105" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J105" s="22" t="s">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K105" s="22" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="106" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J106" s="22" t="s">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K106" s="22" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="107" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J107" s="19" t="s">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K107" s="19" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="108" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J108" s="13" t="s">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K108" s="13" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="109" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J109" s="17" t="s">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K109" s="17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="110" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J110" s="17" t="s">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K110" s="17" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="111" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J111" s="17" t="s">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K111" s="17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J112" t="s">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K112" t="s">
         <v>439</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+  <conditionalFormatting sqref="A1:A21 A23:A1048576">
+    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A22">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+  <conditionalFormatting sqref="A2:A21">
+    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A79 A24:A53">
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+  <conditionalFormatting sqref="A78 A23:A52">
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A79 A48:A53 A23:A44">
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
+  <conditionalFormatting sqref="A78 A47:A52 A23:A43">
+    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A80 A54:A60">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  <conditionalFormatting sqref="A79 A53:A59">
+    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A80 A54:A66">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+  <conditionalFormatting sqref="A79 A53:A65">
+    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A80 A54:A78">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  <conditionalFormatting sqref="A79 A53:A77">
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A89:A1048576 A1:A83">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="A86:A1048576 A1:A21 A23:A84">
+    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J74">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="A89:A1048576 A1:A21 A23:A82">
+    <cfRule type="duplicateValues" dxfId="14" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K74">
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J97:J100" xr:uid="{9B470692-B427-084C-9A15-88859E03855C}">
-      <formula1>$J$2:$J$216</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K97:K100" xr:uid="{9B470692-B427-084C-9A15-88859E03855C}">
+      <formula1>$K$2:$K$216</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A84:A88 E70" xr:uid="{E1CFB512-ECCD-2E47-A882-77566D3BFDE2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E69" xr:uid="{E1CFB512-ECCD-2E47-A882-77566D3BFDE2}">
       <formula1>$A$2:$A$88</formula1>
     </dataValidation>
   </dataValidations>
@@ -29173,34 +29444,34 @@
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A22">
-    <cfRule type="duplicateValues" dxfId="23" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A24:A53">
-    <cfRule type="duplicateValues" dxfId="22" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A48:A53 A23:A44">
-    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80 A54:A60">
-    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80 A54:A66">
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80 A54:A78">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A89:A1048576 A1:A83">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J74">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A84:A88 E70" xr:uid="{E4B0464D-5463-D94C-8BC4-48A43EC9048B}">
@@ -29633,7 +29904,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A28">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
